--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Spaceman Spiff</v>
+        <v>Kid Onion Alien</v>
       </c>
       <c r="B2">
-        <v>1277</v>
+        <v>1036</v>
       </c>
       <c r="C2" t="str">
-        <v>filbertgillis</v>
+        <v>myndzi</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Kid Onion Alien</v>
+        <v>Spellbinder</v>
       </c>
       <c r="B2">
-        <v>1036</v>
+        <v>1406</v>
       </c>
       <c r="C2" t="str">
-        <v>myndzi</v>
+        <v>softlump</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Spellbinder</v>
+        <v>Baby Gao</v>
       </c>
       <c r="B2">
-        <v>1406</v>
+        <v>1397</v>
       </c>
       <c r="C2" t="str">
-        <v>softlump</v>
+        <v>flippy826</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Baby Gao</v>
+        <v>Sweaty Diver</v>
       </c>
       <c r="B2">
-        <v>1397</v>
+        <v>1475</v>
       </c>
       <c r="C2" t="str">
-        <v>flippy826</v>
+        <v>thefishtaco</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -418,7 +418,7 @@
         <v>1475</v>
       </c>
       <c r="C2" t="str">
-        <v>thefishtaco</v>
+        <v>fishtaco(uses weird text)</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Sweaty Diver</v>
+        <v>Zorro</v>
       </c>
       <c r="B2">
-        <v>1475</v>
+        <v>1490</v>
       </c>
       <c r="C2" t="str">
-        <v>fishtaco(uses weird text)</v>
+        <v>oobusk</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Zorro</v>
+        <v>Kolmisilma</v>
       </c>
       <c r="B2">
-        <v>1490</v>
+        <v>1507</v>
       </c>
       <c r="C2" t="str">
-        <v>oobusk</v>
+        <v>rionad</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -418,7 +418,7 @@
         <v>1507</v>
       </c>
       <c r="C2" t="str">
-        <v>rionad</v>
+        <v>rionnad</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Kolmisilma</v>
+        <v>Spartan</v>
       </c>
       <c r="B2">
-        <v>1507</v>
+        <v>854</v>
       </c>
       <c r="C2" t="str">
-        <v>rionnad</v>
+        <v>nolava</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Spartan</v>
+        <v>noita crown and amulet</v>
       </c>
       <c r="B2">
-        <v>854</v>
+        <v>1170</v>
       </c>
       <c r="C2" t="str">
-        <v>nolava</v>
+        <v>maito1794</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>noita crown and amulet</v>
+        <v>Tenna</v>
       </c>
       <c r="B2">
-        <v>1170</v>
+        <v>1626</v>
       </c>
       <c r="C2" t="str">
-        <v>maito1794</v>
+        <v>virtualbutt_</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Tenna</v>
+        <v>Ming Ming</v>
       </c>
       <c r="B2">
-        <v>1626</v>
+        <v>946</v>
       </c>
       <c r="C2" t="str">
-        <v>virtualbutt_</v>
+        <v>any_one_plz</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ming Ming</v>
+        <v>Helldiver Helmet</v>
       </c>
       <c r="B2">
-        <v>946</v>
+        <v>1213</v>
       </c>
       <c r="C2" t="str">
-        <v>any_one_plz</v>
+        <v>snekiecr8</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Helldiver Helmet</v>
+        <v>Aries Horns</v>
       </c>
       <c r="B2">
-        <v>1213</v>
+        <v>829</v>
       </c>
       <c r="C2" t="str">
-        <v>snekiecr8</v>
+        <v>taianvor</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Aries Horns</v>
+        <v>Lagavulin Hat</v>
       </c>
       <c r="B2">
-        <v>829</v>
+        <v>1433</v>
       </c>
       <c r="C2" t="str">
-        <v>taianvor</v>
+        <v>greczko77</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Lagavulin Hat</v>
+        <v>Jimbo</v>
       </c>
       <c r="B2">
-        <v>1433</v>
+        <v>1600</v>
       </c>
       <c r="C2" t="str">
-        <v>greczko77</v>
+        <v>kzmz_syndicate</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jimbo</v>
+        <v xml:space="preserve">Cartethiya </v>
       </c>
       <c r="B2">
-        <v>1600</v>
+        <v>1530</v>
       </c>
       <c r="C2" t="str">
-        <v>kzmz_syndicate</v>
+        <v>hermaeu</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v xml:space="preserve">Cartethiya </v>
+        <v>Beach set?</v>
       </c>
       <c r="B2">
-        <v>1530</v>
+        <v>1348</v>
       </c>
       <c r="C2" t="str">
-        <v>hermaeu</v>
+        <v>peterce3</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Beach set?</v>
+        <v>Chiikawa</v>
       </c>
       <c r="B2">
-        <v>1348</v>
+        <v>1671</v>
       </c>
       <c r="C2" t="str">
-        <v>peterce3</v>
+        <v>superpapipig</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Chiikawa</v>
+        <v>Completely not suspicious at all hat - Blue</v>
       </c>
       <c r="B2">
-        <v>1671</v>
+        <v>1163</v>
       </c>
       <c r="C2" t="str">
-        <v>superpapipig</v>
+        <v>miczupl</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Completely not suspicious at all hat - Blue</v>
+        <v>AIO Cooler</v>
       </c>
       <c r="B2">
-        <v>1163</v>
+        <v>1656</v>
       </c>
       <c r="C2" t="str">
-        <v>miczupl</v>
+        <v>kuuucki</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AIO Cooler</v>
+        <v>Water Princess</v>
       </c>
       <c r="B2">
-        <v>1656</v>
+        <v>1003</v>
       </c>
       <c r="C2" t="str">
-        <v>kuuucki</v>
+        <v>viowlet</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Water Princess</v>
+        <v>Garen (Hair and Pauldrons)</v>
       </c>
       <c r="B2">
-        <v>1003</v>
+        <v>1294</v>
       </c>
       <c r="C2" t="str">
-        <v>viowlet</v>
+        <v>vexilus_</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Garen (Hair and Pauldrons)</v>
+        <v>Falcon</v>
       </c>
       <c r="B2">
-        <v>1294</v>
+        <v>1540</v>
       </c>
       <c r="C2" t="str">
-        <v>vexilus_</v>
+        <v>shrimp_commander</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Falcon</v>
+        <v>Galaxy Brain</v>
       </c>
       <c r="B2">
-        <v>1540</v>
+        <v>1670</v>
       </c>
       <c r="C2" t="str">
-        <v>shrimp_commander</v>
+        <v>shankmo</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Galaxy Brain</v>
+        <v>Ryuu Lion</v>
       </c>
       <c r="B2">
-        <v>1670</v>
+        <v>1346</v>
       </c>
       <c r="C2" t="str">
-        <v>shankmo</v>
+        <v>redkelly_</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ryuu Lion</v>
+        <v>Avatar Pavi</v>
       </c>
       <c r="B2">
-        <v>1346</v>
+        <v>1547</v>
       </c>
       <c r="C2" t="str">
-        <v>redkelly_</v>
+        <v>flashfastblack</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Avatar Pavi</v>
+        <v>Voli</v>
       </c>
       <c r="B2">
-        <v>1547</v>
+        <v>1398</v>
       </c>
       <c r="C2" t="str">
-        <v>flashfastblack</v>
+        <v>flippy826</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Voli</v>
+        <v>PLAYERUNKNOWN Skin</v>
       </c>
       <c r="B2">
-        <v>1398</v>
+        <v>862</v>
       </c>
       <c r="C2" t="str">
-        <v>flippy826</v>
+        <v>nolava</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>PLAYERUNKNOWN Skin</v>
+        <v>Bacon Hair</v>
       </c>
       <c r="B2">
-        <v>862</v>
+        <v>1587</v>
       </c>
       <c r="C2" t="str">
-        <v>nolava</v>
+        <v>juansteed</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Bacon Hair</v>
+        <v>Cone of shame</v>
       </c>
       <c r="B2">
-        <v>1587</v>
+        <v>1194</v>
       </c>
       <c r="C2" t="str">
-        <v>juansteed</v>
+        <v>maito1794</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Cone of shame</v>
+        <v>Crab Hat</v>
       </c>
       <c r="B2">
-        <v>1194</v>
+        <v>1609</v>
       </c>
       <c r="C2" t="str">
-        <v>maito1794</v>
+        <v>oobusk</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Crab Hat</v>
+        <v>Rose</v>
       </c>
       <c r="B2">
-        <v>1609</v>
+        <v>831</v>
       </c>
       <c r="C2" t="str">
-        <v>oobusk</v>
+        <v>taianvor</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Rose</v>
+        <v>Altar Set</v>
       </c>
       <c r="B2">
-        <v>831</v>
+        <v>1427</v>
       </c>
       <c r="C2" t="str">
-        <v>taianvor</v>
+        <v>snekiecr8</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Altar Set</v>
+        <v>Tuck</v>
       </c>
       <c r="B2">
-        <v>1427</v>
+        <v>947</v>
       </c>
       <c r="C2" t="str">
-        <v>snekiecr8</v>
+        <v>any_one_plz</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Tuck</v>
+        <v>Coraline</v>
       </c>
       <c r="B2">
-        <v>947</v>
+        <v>1329</v>
       </c>
       <c r="C2" t="str">
-        <v>any_one_plz</v>
+        <v>filbertgillis</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Coraline</v>
+        <v>Kafka Hibino</v>
       </c>
       <c r="B2">
-        <v>1329</v>
+        <v>1421</v>
       </c>
       <c r="C2" t="str">
-        <v>filbertgillis</v>
+        <v>untoldst0ry</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Kafka Hibino</v>
+        <v>Urahara Kisuke Hat</v>
       </c>
       <c r="B2">
-        <v>1421</v>
+        <v>1571</v>
       </c>
       <c r="C2" t="str">
-        <v>untoldst0ry</v>
+        <v>oberonsskills</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Urahara Kisuke Hat</v>
+        <v>Dark Halo</v>
       </c>
       <c r="B2">
-        <v>1571</v>
+        <v>1739</v>
       </c>
       <c r="C2" t="str">
-        <v>oberonsskills</v>
+        <v>indoorcat_</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Dark Halo</v>
+        <v>Sherma</v>
       </c>
       <c r="B2">
-        <v>1739</v>
+        <v>1658</v>
       </c>
       <c r="C2" t="str">
-        <v>indoorcat_</v>
+        <v>evil_moo</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Sherma</v>
+        <v>Broken Image Icon</v>
       </c>
       <c r="B2">
-        <v>1658</v>
+        <v>1617</v>
       </c>
       <c r="C2" t="str">
-        <v>evil_moo</v>
+        <v>koboldneep</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,10 +412,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Broken Image Icon</v>
+        <v>Ironclad</v>
       </c>
       <c r="B2">
-        <v>1617</v>
+        <v>1644</v>
       </c>
       <c r="C2" t="str">
         <v>koboldneep</v>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ironclad</v>
+        <v>Brewman</v>
       </c>
       <c r="B2">
-        <v>1644</v>
+        <v>1766</v>
       </c>
       <c r="C2" t="str">
-        <v>koboldneep</v>
+        <v>grimhof</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,7 +412,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Brewman</v>
+        <v>Brewman (links are messed up, grabbed from discord instead)</v>
       </c>
       <c r="B2">
         <v>1766</v>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Brewman (links are messed up, grabbed from discord instead)</v>
+        <v>Ponyo</v>
       </c>
       <c r="B2">
-        <v>1766</v>
+        <v>1653</v>
       </c>
       <c r="C2" t="str">
-        <v>grimhof</v>
+        <v>oceantree_</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ponyo</v>
+        <v>Sonia</v>
       </c>
       <c r="B2">
-        <v>1653</v>
+        <v>897</v>
       </c>
       <c r="C2" t="str">
-        <v>oceantree_</v>
+        <v>nolava</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,10 +412,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Sonia</v>
+        <v>Grim</v>
       </c>
       <c r="B2">
-        <v>897</v>
+        <v>927</v>
       </c>
       <c r="C2" t="str">
         <v>nolava</v>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Grim</v>
+        <v>Braum</v>
       </c>
       <c r="B2">
-        <v>927</v>
+        <v>1295</v>
       </c>
       <c r="C2" t="str">
-        <v>nolava</v>
+        <v>vexilus_</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_info.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_info.xlsx
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Braum</v>
+        <v>Fly Agaric Hat + Minecraft soil</v>
       </c>
       <c r="B2">
-        <v>1295</v>
+        <v>1679</v>
       </c>
       <c r="C2" t="str">
-        <v>vexilus_</v>
+        <v>miczupl</v>
       </c>
     </row>
   </sheetData>
